--- a/voyage_data.xlsx
+++ b/voyage_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6298,6 +6298,90 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>82</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ABP49</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Академик Борис Петров</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>49</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2022-06-23</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Дудков И.Ю.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>SeaBat T50</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>6190001111928</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>DTM, ESRI ASCII, CSV</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>96.2 Gb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/voyage_data.xlsx
+++ b/voyage_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T137"/>
+  <dimension ref="A1:T162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -978,29 +978,69 @@
       <c r="E8" t="n">
         <v>39</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>11.05.2019</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>20.05.2019</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>6190001111732</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>PDS2000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>80.7 Gb</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1024,35 +1064,67 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2019-08-17</t>
+          <t>17.08.2019</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>27.08.2019</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>6190001111732</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>PDS2000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>126 Gb</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1074,29 +1146,69 @@
       <c r="E10" t="n">
         <v>43</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>21.09.2019</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>09.10.2019</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Дорохова Е.В.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>6190001111732</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Атлантика</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Qinsy project</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>31.9 Gb</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2142,7 +2254,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Фрей Дмитрий Ильич</t>
+          <t>Фрей Д.И.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -8091,7 +8203,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Фрей Дмитрий Ильич</t>
+          <t>Фрей Д.И.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8175,7 +8287,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Фрей Дмитрий Ильич</t>
+          <t>Фрей Д.И.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8259,7 +8371,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Фрей Дмитрий Ильич</t>
+          <t>Фрей Д.И.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8957,12 +9069,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>27.07.2021</t>
+          <t>16.09.2021</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>07.08.2021</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8981,7 +9093,11 @@
       <c r="K109" t="n">
         <v>6190001113043</v>
       </c>
-      <c r="L109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Луговой Н.Н.</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
@@ -9037,12 +9153,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>27.07.2021</t>
+          <t>16.09.2021</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>07.08.2021</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -9061,7 +9177,11 @@
       <c r="K110" t="n">
         <v>6190001113043</v>
       </c>
-      <c r="L110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Луговой Н.Н.</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
@@ -9117,12 +9237,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>27.07.2021</t>
+          <t>16.09.2021</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>07.08.2021</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -9141,7 +9261,11 @@
       <c r="K111" t="n">
         <v>6190001113043</v>
       </c>
-      <c r="L111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Луговой Н.Н.</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
@@ -9197,12 +9321,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>27.07.2021</t>
+          <t>16.09.2021</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>07.08.2021</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9221,7 +9345,11 @@
       <c r="K112" t="n">
         <v>6190001113043</v>
       </c>
-      <c r="L112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Луговой Н.Н.</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
@@ -9277,12 +9405,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>27.07.2021</t>
+          <t>16.09.2021</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>07.08.2021</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9301,7 +9429,11 @@
       <c r="K113" t="n">
         <v>0</v>
       </c>
-      <c r="L113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Луговой Н.Н.</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
@@ -9357,12 +9489,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>27.07.2021</t>
+          <t>16.09.2021</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>07.08.2021</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9381,7 +9513,11 @@
       <c r="K114" t="n">
         <v>0</v>
       </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Луговой Н.Н.</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
@@ -9437,12 +9573,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>27.07.2021</t>
+          <t>16.09.2021</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>07.08.2021</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -9461,7 +9597,11 @@
       <c r="K115" t="n">
         <v>0</v>
       </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Луговой Н.Н.</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
@@ -9517,12 +9657,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>27.07.2021</t>
+          <t>16.09.2021</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>07.08.2021</t>
+          <t>05.10.2021</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9541,7 +9681,11 @@
       <c r="K116" t="n">
         <v>0</v>
       </c>
-      <c r="L116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Луговой Н.Н.</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
@@ -11265,15 +11409,19 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>13.10.2018</t>
+          <t>05.10.2018</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>29.10.2018</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
+          <t>30.10.2018</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="n">
         <v>2</v>
@@ -11281,7 +11429,11 @@
       <c r="K137" t="n">
         <v>6190001111732</v>
       </c>
-      <c r="L137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
@@ -11312,6 +11464,2050 @@
       <c r="T137" t="inlineStr">
         <is>
           <t>18.4  Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ABP44</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Академик Борис Петров</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>44</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>05.10.2018</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>30.10.2018</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>2</v>
+      </c>
+      <c r="K138" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Hypack projects</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>35.7  Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ABP44</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Академик Борис Петров</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>44</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>05.10.2018</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>30.10.2018</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>2</v>
+      </c>
+      <c r="K139" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Видео</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Супер ГНОМ</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>MPG</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>1.67  Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Лодка "Бриг"</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>02.11.2018</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>02.11.2018</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>2</v>
+      </c>
+      <c r="K140" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>ЛПС, АО ИО РАН</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>ЮВБ, Вислинская коса</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>эхолот GARMIN</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>RAW, GIS project, SVP, *.xlsx</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>8.47 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Лодка "Бриг"</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>09.11.2018</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>09.11.2018</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>2</v>
+      </c>
+      <c r="K141" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>ЛПС, АО ИО РАН</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>ЮВБ, Янтарный</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>эхолот GARMIN</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>RAW, GIS project, SVP, *.xlsx</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>8.63 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Тунобот "Норд 3"</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>15.11.2018</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>16.11.2018</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>2</v>
+      </c>
+      <c r="K142" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ЛПС, АО ИО РАН</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>ЮВБ, Зеленоградск</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Konsberg EA-400</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>RAW, GIS project, SVP, *.xlsx</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>38 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Тунобот "Норд 3"</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>07.11.2018</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>07.11.2018</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>2</v>
+      </c>
+      <c r="K143" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>ЛПС, АО ИО РАН</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>ЮВБ, Отрадное</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Konsberg EA-400</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>RAW, GIS project, SVP, *.xlsx</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>7.1 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Тунобот "Норд 3"</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>11.10.2018</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>11.10.2018</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>2</v>
+      </c>
+      <c r="K144" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>ЛПС, АО ИО РАН</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>ЮВБ, Пионерский</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Konsberg EA-400</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>RAW, GIS project, SVP, *.xlsx</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>7.98 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Тунобот "Норд 3"</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>15.11.2018</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>15.11.2018</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>2</v>
+      </c>
+      <c r="K145" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>ЛПС, АО ИО РАН</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>ЮВБ, Рыбачий</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Konsberg EA-400</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>RAW, GIS project, SVP, *.xlsx</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>24.2 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>2</v>
+      </c>
+      <c r="K146" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>ЛПС, АО ИО РАН</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>ЮВБ, прибрежные зоны</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Konsberg EA-400</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Hypack project</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>1.22 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Тунобот "Норд 3"</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>08.11.2018</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>09.11.2018</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>2</v>
+      </c>
+      <c r="K147" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>ЮВБ, м.Таран</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Hypack project</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>3.33 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ANS39</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>39</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>11.05.2019</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>20.05.2019</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>2</v>
+      </c>
+      <c r="K148" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>FZ</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>PDS2000</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>63.4 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ANS39</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>39</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>11.05.2019</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20.05.2019</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>2</v>
+      </c>
+      <c r="K149" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>SEB, FZ</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>GSF, XTF, XYZ</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>14.9 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ANS39</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>39</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>11.05.2019</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20.05.2019</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>2</v>
+      </c>
+      <c r="K150" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>SEB, FZ</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>JSF, SEG-Y</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>22.3 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ANS39</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>39</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>11.05.2019</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>20.05.2019</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>2</v>
+      </c>
+      <c r="K151" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>SEB, FZ</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>SVP, CTD, NAV</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>33 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ANS39</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>39</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>11.05.2019</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20.05.2019</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>2</v>
+      </c>
+      <c r="K152" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>SEB, FZ</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>130 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ANS42</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>42</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>17.08.2019</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>27.08.2019</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>2</v>
+      </c>
+      <c r="K153" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>PDS2000</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>132 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ANS42</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>42</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>17.08.2019</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>27.08.2019</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>2</v>
+      </c>
+      <c r="K154" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>XTF</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>14.5 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ANS42</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>42</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>17.08.2019</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>27.08.2019</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>2</v>
+      </c>
+      <c r="K155" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>JSF</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>3.9 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ANS42</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>42</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>17.08.2019</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>27.08.2019</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>2</v>
+      </c>
+      <c r="K156" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>3.09 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ANS42</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>42</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>17.08.2019</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>27.08.2019</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>2</v>
+      </c>
+      <c r="K157" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>CTD, SVP</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>11.7 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ANS43</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>43</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>21.09.2019</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>09.10.2019</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Дорохова Е.В.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>2</v>
+      </c>
+      <c r="K158" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Атлантика</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>XTF</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>2.68 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ANS43</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>43</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>21.09.2019</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>09.10.2019</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Дорохова Е.В.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>2</v>
+      </c>
+      <c r="K159" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Атлантика</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>JSF, SEG-Y</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>11.9 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ANS43</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>43</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>21.09.2019</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>09.10.2019</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Дорохова Е.В.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>2</v>
+      </c>
+      <c r="K160" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Атлантика</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Hypack project</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>44.1 Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ANS43</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>43</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>21.09.2019</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>09.10.2019</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Дорохова Е.В.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>2</v>
+      </c>
+      <c r="K161" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Атлантика</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>CTD, SVP, журналы, отчет</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>16.8 Mb</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ANS43</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>43</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>21.09.2019</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>09.10.2019</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Дорохова Е.В.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>2</v>
+      </c>
+      <c r="K162" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Атлантика</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>81.9 Mb</t>
         </is>
       </c>
     </row>

--- a/voyage_data.xlsx
+++ b/voyage_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T178"/>
+  <dimension ref="A1:U232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,13 +529,18 @@
           <t>Объем данных</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>UID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -552,42 +557,79 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2017-10-24</t>
+          <t>02.08.2016</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2017-10-27</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>16.09.2016</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Пака В.Т.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>6190001111735</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>SEB. Борнхольмский, Слупский, Гданьский бассейны</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Hypack project, PrintScreen, журналы</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>7.48 Gb</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1_7e14c3b5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -602,29 +644,74 @@
       <c r="E3" t="n">
         <v>33</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>18.10.2016</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>26.12.2016</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Сивков В.В.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>6190001111735</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Сухих Е.А.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Атлантика, Балтика</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>JSF, SEG-Y, PrintScreen, журналы</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2_1244d93d</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -705,6 +792,11 @@
           <t>18.2 Gb</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3_54f7a319</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -771,7 +863,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -787,6 +879,11 @@
       <c r="T5" t="inlineStr">
         <is>
           <t>27.8 Gb</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4_bd3008d2</t>
         </is>
       </c>
     </row>
@@ -873,6 +970,11 @@
           <t>19.1 Gb</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5_85dec35e</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -939,7 +1041,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -955,6 +1057,11 @@
       <c r="T7" t="inlineStr">
         <is>
           <t>41.8 Gb</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>6_00563b7f</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1130,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1039,6 +1146,11 @@
       <c r="T8" t="inlineStr">
         <is>
           <t>80.7 Gb</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>7_3bdf4010</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1219,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1123,6 +1235,11 @@
       <c r="T9" t="inlineStr">
         <is>
           <t>126 Gb</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>8_2e21da23</t>
         </is>
       </c>
     </row>
@@ -1209,6 +1326,11 @@
           <t>31.9 Gb</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>9_4e232004</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1293,6 +1415,11 @@
           <t>14.1 Gb</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>10_6f6e6dbf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1359,7 +1486,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1375,6 +1502,11 @@
       <c r="T12" t="inlineStr">
         <is>
           <t>13.7  Gb</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>11_c9bc95f9</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1515,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2020</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1398,73 +1530,163 @@
       <c r="E13" t="n">
         <v>47</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>25.06.2020</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>04.07.2020</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>6190001111732</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Reson Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>PDS2000 project, Qinsy project, XTF</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>633 Gb</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>12_c51adcd2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANS54</t>
+          <t>PSH135</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Академик Николай Страхов</t>
+          <t>Профессор Штокман</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+        <v>135</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>03.04.2017</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>07.04.2017</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>6190001111735</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>SyQuest Bathy-2010</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ODC, CSV</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>423  Mb</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>13_c733cdf8</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1549,6 +1771,11 @@
           <t>914 Gb</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>14_ce922dc4</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1633,6 +1860,11 @@
           <t>256 Gb</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>15_7b3fd70a</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1699,7 +1931,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1715,6 +1947,11 @@
       <c r="T17" t="inlineStr">
         <is>
           <t>2.05 Tb</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>16_34095f41</t>
         </is>
       </c>
     </row>
@@ -1783,7 +2020,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1799,6 +2036,11 @@
       <c r="T18" t="inlineStr">
         <is>
           <t>1.27 Tb</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>17_febe0176</t>
         </is>
       </c>
     </row>
@@ -1867,7 +2109,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1883,6 +2125,11 @@
       <c r="T19" t="inlineStr">
         <is>
           <t>2.85 Tb</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>18_3034c776</t>
         </is>
       </c>
     </row>
@@ -1951,7 +2198,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1967,6 +2214,11 @@
       <c r="T20" t="inlineStr">
         <is>
           <t>1.28 Tb</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>19_efeda9ba</t>
         </is>
       </c>
     </row>
@@ -2053,6 +2305,11 @@
           <t>74.3 Gb</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>20_34b73508</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2129,13 +2386,18 @@
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>21_b8664100</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2020</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2150,29 +2412,74 @@
       <c r="E23" t="n">
         <v>56</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>19.08.2020</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>28.08.2020</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ульянова М.О.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>6190001111732</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ, ИЭЗ Польши, ИЭЗ Швеции</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>SES2000</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>RAW, SES, SEG-Y, PrintScreen, журналы</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>75.8 Gb</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>22_3118e5b6</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2217,6 +2524,11 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>23_c17de6f4</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2301,6 +2613,11 @@
           <t>400 Gb</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>24_0ee50bcf</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2385,6 +2702,11 @@
           <t>1.2 Tb</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>25_875e24a8</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2451,7 +2773,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2467,6 +2789,11 @@
       <c r="T27" t="inlineStr">
         <is>
           <t>2.37 Tb</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>26_c61a8811</t>
         </is>
       </c>
     </row>
@@ -2553,6 +2880,11 @@
           <t>251 Gb</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>27_fd7d9cfa</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2619,7 +2951,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2635,6 +2967,11 @@
       <c r="T29" t="inlineStr">
         <is>
           <t>280 Gb</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>28_992259d2</t>
         </is>
       </c>
     </row>
@@ -2721,6 +3058,11 @@
           <t>75.5 Gb</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>29_e9e6b2a8</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2787,7 +3129,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2803,6 +3145,11 @@
       <c r="T31" t="inlineStr">
         <is>
           <t>225 Gb ;  339 Gb</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>30_c7ba9c0b</t>
         </is>
       </c>
     </row>
@@ -2887,6 +3234,11 @@
       <c r="T32" t="inlineStr">
         <is>
           <t>40.5 Gb</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>31_8c8b3e34</t>
         </is>
       </c>
     </row>
@@ -2941,6 +3293,11 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>32_00241b2e</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2993,6 +3350,11 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>33_3424e007</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3059,7 +3421,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Konsberg EA-400</t>
+          <t>Kongsberg Simrad EA400</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3075,6 +3437,11 @@
       <c r="T35" t="inlineStr">
         <is>
           <t>13.2  Gb</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>34_98513e20</t>
         </is>
       </c>
     </row>
@@ -3121,6 +3488,11 @@
           <t>797  Mb</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>35_79e6e534</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3165,6 +3537,11 @@
           <t>797 Mb</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>36_98c8cae7</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3231,7 +3608,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3247,6 +3624,11 @@
       <c r="T38" t="inlineStr">
         <is>
           <t>1.02 Tb ;  1.35 Tb</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>37_8bffa421</t>
         </is>
       </c>
     </row>
@@ -3333,6 +3715,11 @@
           <t>215 Gb</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>38_053f8e1d</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3399,7 +3786,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3415,6 +3802,11 @@
       <c r="T40" t="inlineStr">
         <is>
           <t>280 Gb</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>39_972b1e4e</t>
         </is>
       </c>
     </row>
@@ -3501,6 +3893,11 @@
           <t>75.5 Gb</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>40_f2de6103</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3567,7 +3964,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3583,6 +3980,11 @@
       <c r="T42" t="inlineStr">
         <is>
           <t>225 Gb ;  339 Gb</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>41_fec817a1</t>
         </is>
       </c>
     </row>
@@ -3669,6 +4071,11 @@
           <t>40.5 Gb</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>42_62a805ae</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3753,6 +4160,11 @@
           <t>74.3 Gb</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>43_73f51df3</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3819,7 +4231,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3835,6 +4247,11 @@
       <c r="T45" t="inlineStr">
         <is>
           <t>2.86 Tb</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>44_9d53fa3f</t>
         </is>
       </c>
     </row>
@@ -3903,7 +4320,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -3919,6 +4336,11 @@
       <c r="T46" t="inlineStr">
         <is>
           <t>1.29 Tb</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>45_f7eb1ac7</t>
         </is>
       </c>
     </row>
@@ -3987,7 +4409,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4003,6 +4425,11 @@
       <c r="T47" t="inlineStr">
         <is>
           <t>41.2 Gb</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>46_01c34013</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4498,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4087,6 +4514,11 @@
       <c r="T48" t="inlineStr">
         <is>
           <t>8.39 Gb</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>47_23e7b96b</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4587,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4171,6 +4603,11 @@
       <c r="T49" t="inlineStr">
         <is>
           <t>11.9 Gb, 33.3 Gb</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>48_c64d286e</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4676,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4255,6 +4692,11 @@
       <c r="T50" t="inlineStr">
         <is>
           <t>3.09 Gb, 9.96 Gb</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>49_ea556b06</t>
         </is>
       </c>
     </row>
@@ -4341,6 +4783,11 @@
           <t>540 Mb</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>50_fbf08f29</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4425,6 +4872,11 @@
           <t>50.6 Gb</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>51_404264c2</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4511,6 +4963,11 @@
       <c r="T53" t="inlineStr">
         <is>
           <t>9.96 Gb</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>52_9fd46ac6</t>
         </is>
       </c>
     </row>
@@ -4593,6 +5050,11 @@
           <t>235 Мb</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>53_e547d7a9</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4659,7 +5121,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -4675,6 +5137,11 @@
       <c r="T55" t="inlineStr">
         <is>
           <t>521 Gb</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>54_9574e668</t>
         </is>
       </c>
     </row>
@@ -4743,7 +5210,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -4759,6 +5226,11 @@
       <c r="T56" t="inlineStr">
         <is>
           <t>1.71 Tb</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>55_82af807e</t>
         </is>
       </c>
     </row>
@@ -4845,6 +5317,11 @@
           <t>396 Gb</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>56_fc6aca0a</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4911,7 +5388,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -4927,6 +5404,11 @@
       <c r="T58" t="inlineStr">
         <is>
           <t>1.12 Tb</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>57_8b8cfb56</t>
         </is>
       </c>
     </row>
@@ -5013,6 +5495,11 @@
           <t>222 Gb</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>58_6b56c4c9</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5097,6 +5584,11 @@
           <t>540 Mb</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>59_efb54cb7</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5181,6 +5673,11 @@
           <t>50.6 Gb</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>60_7a2b8e82</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5267,6 +5764,11 @@
       <c r="T62" t="inlineStr">
         <is>
           <t>9.96 Gb</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>61_0dcfe4fd</t>
         </is>
       </c>
     </row>
@@ -5349,6 +5851,11 @@
           <t>235 Мb</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>62_27838636</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5415,7 +5922,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5431,6 +5938,11 @@
       <c r="T64" t="inlineStr">
         <is>
           <t>521 Gb</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>63_436a58e2</t>
         </is>
       </c>
     </row>
@@ -5499,7 +6011,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5515,6 +6027,11 @@
       <c r="T65" t="inlineStr">
         <is>
           <t>1.76 Tb</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>64_0c15d0a3</t>
         </is>
       </c>
     </row>
@@ -5601,6 +6118,11 @@
           <t>396 Gb</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>65_65955ad2</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5667,7 +6189,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -5683,6 +6205,11 @@
       <c r="T67" t="inlineStr">
         <is>
           <t>1.12 Tb</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>66_057c520c</t>
         </is>
       </c>
     </row>
@@ -5769,6 +6296,11 @@
           <t>294 Gb</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>67_6b04ad47</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5853,6 +6385,11 @@
           <t>636 Gb</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>68_cfd831a7</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5919,7 +6456,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -5935,6 +6472,11 @@
       <c r="T70" t="inlineStr">
         <is>
           <t>3.21 Tb</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>69_f606cab9</t>
         </is>
       </c>
     </row>
@@ -6021,6 +6563,11 @@
           <t>1.58 Gb</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>70_6922a593</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6105,6 +6652,11 @@
           <t>636 Gb</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>71_5908efd5</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6171,7 +6723,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6187,6 +6739,11 @@
       <c r="T73" t="inlineStr">
         <is>
           <t>3.21 Tb</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>72_2b1992d0</t>
         </is>
       </c>
     </row>
@@ -6273,6 +6830,11 @@
           <t>1.58 Gb</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>73_5a5cc4d3</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6361,6 +6923,11 @@
           <t>11.0  Gb</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>74_7527ced7</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6449,6 +7016,11 @@
           <t>472  Gb</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>75_4c218cab</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6519,7 +7091,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -6535,6 +7107,11 @@
       <c r="T77" t="inlineStr">
         <is>
           <t>773 Gb</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>76_bc14a3c2</t>
         </is>
       </c>
     </row>
@@ -6621,6 +7198,11 @@
           <t>1.14 Tb</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>77_5f6a0f79</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6687,7 +7269,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -6703,6 +7285,11 @@
       <c r="T79" t="inlineStr">
         <is>
           <t>369 Gb</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>78_d41d0b04</t>
         </is>
       </c>
     </row>
@@ -6775,7 +7362,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -6791,6 +7378,11 @@
       <c r="T80" t="inlineStr">
         <is>
           <t>96.2 Gb</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>79_8c5dcf67</t>
         </is>
       </c>
     </row>
@@ -6863,7 +7455,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -6879,6 +7471,11 @@
       <c r="T81" t="inlineStr">
         <is>
           <t>4.44 Tb</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>80_3a1f4ef2</t>
         </is>
       </c>
     </row>
@@ -6969,6 +7566,11 @@
           <t>472  Gb</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>81_78a50687</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7057,6 +7659,11 @@
           <t>11.0  Gb</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>82_d0254913</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7145,6 +7752,11 @@
           <t>103  Gb</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>83_69b6e372</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7215,7 +7827,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -7231,6 +7843,11 @@
       <c r="T85" t="inlineStr">
         <is>
           <t>130 Gb</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>84_1eca02ef</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7920,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -7319,6 +7936,11 @@
       <c r="T86" t="inlineStr">
         <is>
           <t>539 Gb</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>85_b20cff5a</t>
         </is>
       </c>
     </row>
@@ -7391,7 +8013,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -7407,6 +8029,11 @@
       <c r="T87" t="inlineStr">
         <is>
           <t>97.7 Mb</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>86_e49476c8</t>
         </is>
       </c>
     </row>
@@ -7479,7 +8106,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -7495,6 +8122,11 @@
       <c r="T88" t="inlineStr">
         <is>
           <t>564  Gb</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>87_a0ecf554</t>
         </is>
       </c>
     </row>
@@ -7567,7 +8199,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -7583,6 +8215,11 @@
       <c r="T89" t="inlineStr">
         <is>
           <t>4.44  Tb</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>88_c9acfe01</t>
         </is>
       </c>
     </row>
@@ -7655,7 +8292,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -7671,6 +8308,11 @@
       <c r="T90" t="inlineStr">
         <is>
           <t>96.2 Gb</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>89_28f076ef</t>
         </is>
       </c>
     </row>
@@ -7743,7 +8385,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -7759,6 +8401,11 @@
       <c r="T91" t="inlineStr">
         <is>
           <t>97.7 Mb</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>90_83809a91</t>
         </is>
       </c>
     </row>
@@ -7849,6 +8496,11 @@
           <t>42,82  Gb</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>91_c73dbc6a</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7937,6 +8589,11 @@
           <t>97.33 Gb</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>92_4f6389df</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8025,6 +8682,11 @@
           <t>10.4  Gb</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>93_4160e658</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8113,6 +8775,11 @@
           <t>216  Gb</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>94_adf7c4aa</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -8206,6 +8873,11 @@
           <t>142 Gb</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>95_722760b4</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8294,6 +8966,11 @@
           <t>34.6 Gb</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>96_ffde540b</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -8378,6 +9055,11 @@
           <t>524 Gb</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>97_201b9449</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8462,6 +9144,11 @@
           <t>236 Gb</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>98_d42351ec</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8544,6 +9231,11 @@
       <c r="T100" t="inlineStr">
         <is>
           <t>19,1 Gb</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>99_4f18aa1e</t>
         </is>
       </c>
     </row>
@@ -8608,7 +9300,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -8624,6 +9316,11 @@
       <c r="T101" t="inlineStr">
         <is>
           <t>1.72 Tb</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>100_ec69ade7</t>
         </is>
       </c>
     </row>
@@ -8706,6 +9403,11 @@
           <t>270 Gb</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>101_de6025ba</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8768,7 +9470,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -8784,6 +9486,11 @@
       <c r="T103" t="inlineStr">
         <is>
           <t>209 Gb</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>102_230a08d7</t>
         </is>
       </c>
     </row>
@@ -8864,6 +9571,11 @@
       <c r="T104" t="inlineStr">
         <is>
           <t>105 Mb</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>103_ebdc8195</t>
         </is>
       </c>
     </row>
@@ -8912,7 +9624,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -8928,6 +9640,11 @@
       <c r="T105" t="inlineStr">
         <is>
           <t>1.26 Tb</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>104_a493213a</t>
         </is>
       </c>
     </row>
@@ -8992,7 +9709,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9008,6 +9725,11 @@
       <c r="T106" t="inlineStr">
         <is>
           <t>1.72 Tb</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>105_f6457f07</t>
         </is>
       </c>
     </row>
@@ -9090,6 +9812,11 @@
           <t>270 Gb</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>106_47f724d2</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9152,7 +9879,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -9168,6 +9895,11 @@
       <c r="T108" t="inlineStr">
         <is>
           <t>209 Gb</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>107_02995d0c</t>
         </is>
       </c>
     </row>
@@ -9254,6 +9986,11 @@
           <t>318 Gb</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>108_a5d6d106</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -9320,7 +10057,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -9336,6 +10073,11 @@
       <c r="T110" t="inlineStr">
         <is>
           <t>2.92 Tb</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>109_397179b9</t>
         </is>
       </c>
     </row>
@@ -9404,7 +10146,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9420,6 +10162,11 @@
       <c r="T111" t="inlineStr">
         <is>
           <t>156 Gb</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>110_8d246194</t>
         </is>
       </c>
     </row>
@@ -9488,7 +10235,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -9504,6 +10251,11 @@
       <c r="T112" t="inlineStr">
         <is>
           <t>12.2  Gb</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>111_764baf34</t>
         </is>
       </c>
     </row>
@@ -9590,6 +10342,11 @@
           <t>318 Gb</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>112_99835a10</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9656,7 +10413,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -9672,6 +10429,11 @@
       <c r="T114" t="inlineStr">
         <is>
           <t>2.92 Tb</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>113_0d4bad61</t>
         </is>
       </c>
     </row>
@@ -9740,7 +10502,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -9756,6 +10518,11 @@
       <c r="T115" t="inlineStr">
         <is>
           <t>153 Gb</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>114_4db507d5</t>
         </is>
       </c>
     </row>
@@ -9824,7 +10591,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>SeaBat T50</t>
+          <t>Reson SeaBat T50</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -9840,6 +10607,11 @@
       <c r="T116" t="inlineStr">
         <is>
           <t>12.2  Gb</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>115_993794ae</t>
         </is>
       </c>
     </row>
@@ -9908,7 +10680,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -9924,6 +10696,11 @@
       <c r="T117" t="inlineStr">
         <is>
           <t>7.21 Gb</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>116_2966397d</t>
         </is>
       </c>
     </row>
@@ -9992,7 +10769,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -10008,6 +10785,11 @@
       <c r="T118" t="inlineStr">
         <is>
           <t>95.6 Gb</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>117_37d95e82</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10858,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -10092,6 +10874,11 @@
       <c r="T119" t="inlineStr">
         <is>
           <t>96.2 Gb</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>118_0e3edd59</t>
         </is>
       </c>
     </row>
@@ -10160,7 +10947,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -10176,6 +10963,11 @@
       <c r="T120" t="inlineStr">
         <is>
           <t>3.8 Gb</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>119_fdaf2b9c</t>
         </is>
       </c>
     </row>
@@ -10244,7 +11036,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -10260,6 +11052,11 @@
       <c r="T121" t="inlineStr">
         <is>
           <t>151.4 Mb</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>120_a231a591</t>
         </is>
       </c>
     </row>
@@ -10346,6 +11143,11 @@
           <t>5.31 Gb</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>121_48922036</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -10430,6 +11232,11 @@
           <t>8.19 Gb</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>122_e49aee7b</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -10514,6 +11321,11 @@
           <t>450 Mb</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>123_f575917c</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -10598,6 +11410,11 @@
           <t>1.15 Gb</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>124_45cbdcf6</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -10682,6 +11499,11 @@
           <t>6.87 Gb</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>125_0c74bc3f</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -10748,7 +11570,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -10764,6 +11586,11 @@
       <c r="T127" t="inlineStr">
         <is>
           <t>267 Mb</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>126_134ff2b8</t>
         </is>
       </c>
     </row>
@@ -10828,7 +11655,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -10844,6 +11671,11 @@
       <c r="T128" t="inlineStr">
         <is>
           <t>254 Mb</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>127_f7360282</t>
         </is>
       </c>
     </row>
@@ -10912,7 +11744,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -10928,6 +11760,11 @@
       <c r="T129" t="inlineStr">
         <is>
           <t>7.21 Gb</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>128_ef432b99</t>
         </is>
       </c>
     </row>
@@ -10996,7 +11833,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -11012,6 +11849,11 @@
       <c r="T130" t="inlineStr">
         <is>
           <t>3.8 Gb</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>129_23fcc519</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11922,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -11096,6 +11938,11 @@
       <c r="T131" t="inlineStr">
         <is>
           <t>157 Mb</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>130_0e1f02e7</t>
         </is>
       </c>
     </row>
@@ -11164,7 +12011,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>SeaBat 8111</t>
+          <t>Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -11180,6 +12027,11 @@
       <c r="T132" t="inlineStr">
         <is>
           <t>2.71 Gb</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>131_fa811297</t>
         </is>
       </c>
     </row>
@@ -11258,6 +12110,11 @@
           <t>12 Gb</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>132_387a92c7</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -11342,6 +12199,11 @@
           <t>54.4  Gb</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>133_32e71e79</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -11426,6 +12288,11 @@
           <t>25.5  Gb</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>134_66c6fe92</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -11510,6 +12377,11 @@
           <t>712  Mb</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>135_d758fa97</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -11572,7 +12444,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Konsberg EA-400</t>
+          <t>Kongsberg Simrad EA400</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -11588,6 +12460,11 @@
       <c r="T137" t="inlineStr">
         <is>
           <t>18.4  Gb</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>136_f547db43</t>
         </is>
       </c>
     </row>
@@ -11670,6 +12547,11 @@
           <t>35.7  Gb</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>137_f555bc22</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11750,6 +12632,11 @@
           <t>1.67  Gb</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>138_ecebc168</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11830,6 +12717,11 @@
           <t>8.47 Mb</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>139_1ff282d9</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11910,6 +12802,11 @@
           <t>8.63 Mb</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>140_94ae527d</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -11972,7 +12869,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Konsberg EA-400</t>
+          <t>Kongsberg Simrad EA400</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -11988,6 +12885,11 @@
       <c r="T142" t="inlineStr">
         <is>
           <t>38 Mb</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>141_2f76badb</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12954,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Konsberg EA-400</t>
+          <t>Kongsberg Simrad EA400</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -12068,6 +12970,11 @@
       <c r="T143" t="inlineStr">
         <is>
           <t>7.1 Mb</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>142_3f0906be</t>
         </is>
       </c>
     </row>
@@ -12132,7 +13039,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Konsberg EA-400</t>
+          <t>Kongsberg Simrad EA400</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -12148,6 +13055,11 @@
       <c r="T144" t="inlineStr">
         <is>
           <t>7.98 Mb</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>143_404f31d1</t>
         </is>
       </c>
     </row>
@@ -12212,7 +13124,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Konsberg EA-400</t>
+          <t>Kongsberg Simrad EA400</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -12228,6 +13140,11 @@
       <c r="T145" t="inlineStr">
         <is>
           <t>24.2 Mb</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>144_bba1f58a</t>
         </is>
       </c>
     </row>
@@ -12280,7 +13197,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Konsberg EA-400</t>
+          <t>Kongsberg Simrad EA400</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -12296,6 +13213,11 @@
       <c r="T146" t="inlineStr">
         <is>
           <t>1.22 Gb</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>145_8acc5922</t>
         </is>
       </c>
     </row>
@@ -12374,6 +13296,11 @@
           <t>3.33 Mb</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>146_79889eb4</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -12440,7 +13367,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -12456,6 +13383,11 @@
       <c r="T148" t="inlineStr">
         <is>
           <t>63.4 Gb</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>147_e9a814ee</t>
         </is>
       </c>
     </row>
@@ -12524,7 +13456,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -12540,6 +13472,11 @@
       <c r="T149" t="inlineStr">
         <is>
           <t>14.9 Gb</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>148_fa01eaad</t>
         </is>
       </c>
     </row>
@@ -12626,6 +13563,11 @@
           <t>22.3 Gb</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>149_77832a7a</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -12692,7 +13634,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -12708,6 +13650,11 @@
       <c r="T151" t="inlineStr">
         <is>
           <t>33 Mb</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>150_b728e2c9</t>
         </is>
       </c>
     </row>
@@ -12776,7 +13723,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -12792,6 +13739,11 @@
       <c r="T152" t="inlineStr">
         <is>
           <t>130 Mb</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>151_d3bc094d</t>
         </is>
       </c>
     </row>
@@ -12860,7 +13812,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -12876,6 +13828,11 @@
       <c r="T153" t="inlineStr">
         <is>
           <t>132 Gb</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>152_487544d0</t>
         </is>
       </c>
     </row>
@@ -12944,7 +13901,7 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -12960,6 +13917,11 @@
       <c r="T154" t="inlineStr">
         <is>
           <t>14.5 Gb</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>153_77879644</t>
         </is>
       </c>
     </row>
@@ -13046,6 +14008,11 @@
           <t>3.9 Gb</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>154_10b59eac</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -13112,7 +14079,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -13128,6 +14095,11 @@
       <c r="T156" t="inlineStr">
         <is>
           <t>3.09 Gb</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>155_d52c2703</t>
         </is>
       </c>
     </row>
@@ -13196,7 +14168,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -13212,6 +14184,11 @@
       <c r="T157" t="inlineStr">
         <is>
           <t>11.7 Mb</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>156_9e3b9375</t>
         </is>
       </c>
     </row>
@@ -13298,6 +14275,11 @@
           <t>2.68 Gb</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>157_02c24a23</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -13382,6 +14364,11 @@
           <t>11.9 Gb</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>158_86ac85d8</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -13466,6 +14453,11 @@
           <t>44.1 Gb</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>159_567639d0</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -13550,6 +14542,11 @@
           <t>16.8 Mb</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>160_1af09dc5</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -13634,6 +14631,11 @@
           <t>81.9 Mb</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>161_99ad715e</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -13718,6 +14720,11 @@
           <t>57.2 Gb</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>162_977524fb</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -13802,6 +14809,11 @@
           <t>1.76 Gb</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>163_a4b493c7</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -13886,6 +14898,11 @@
           <t>36.2 Gb</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>164_e482b2a7</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -13970,6 +14987,11 @@
           <t>270 Mb</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>165_da643440</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -14054,6 +15076,11 @@
           <t>73.1 Gb</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>166_af3265e8</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -14138,6 +15165,11 @@
           <t>1.96 Mb</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>167_6596f269</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -14204,7 +15236,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -14220,6 +15252,11 @@
       <c r="T169" t="inlineStr">
         <is>
           <t>21.8  Gb</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>168_7f3a56a2</t>
         </is>
       </c>
     </row>
@@ -14306,6 +15343,11 @@
           <t>4.74  Gb</t>
         </is>
       </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>169_2a79ea94</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -14390,6 +15432,11 @@
           <t>2.62  Gb</t>
         </is>
       </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>170_c6da377a</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -14456,7 +15503,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -14472,6 +15519,11 @@
       <c r="T172" t="inlineStr">
         <is>
           <t>1.18  Gb</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>171_53de1a5e</t>
         </is>
       </c>
     </row>
@@ -14540,7 +15592,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>Reson SeaBat 8111</t>
+          <t>Reson Reson SeaBat 8111</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -14556,6 +15608,11 @@
       <c r="T173" t="inlineStr">
         <is>
           <t>57.9  Mb</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>172_4c8231cb</t>
         </is>
       </c>
     </row>
@@ -14642,6 +15699,11 @@
           <t>9.22 Gb</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>173_f3673592</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -14708,7 +15770,7 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>EA-600</t>
+          <t>Kongsberg Simrad EA600</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -14724,6 +15786,11 @@
       <c r="T175" t="inlineStr">
         <is>
           <t>5.5  Gb</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>174_540214f4</t>
         </is>
       </c>
     </row>
@@ -14792,7 +15859,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>Konsberg EA-400</t>
+          <t>Kongsberg Simrad EA400</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -14808,6 +15875,11 @@
       <c r="T176" t="inlineStr">
         <is>
           <t>4.09  Gb</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>175_c986b186</t>
         </is>
       </c>
     </row>
@@ -14874,6 +15946,11 @@
           <t>298 Mb</t>
         </is>
       </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>176_7ef934a1</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -14938,6 +16015,4605 @@
           <t>690 Mb</t>
         </is>
       </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>177_9cd2dd66</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Лодка РЖД 09-61 "БРИГ"</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>03.07.2019</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>05.07.2019</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="n">
+        <v>2</v>
+      </c>
+      <c r="K179" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>акватории рек Преголя, Дейма</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Reki2019</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Hypack project</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>20.8 Gb</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>178_a2f911f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Лодка РЖД 09-61 "БРИГ"</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>21.08.2019</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>22.08.2019</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="n">
+        <v>2</v>
+      </c>
+      <c r="K180" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>акватория Калининградского (Вислинского) залива</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Reki2019</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Hypack project</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>20.8 Gb</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>179_039d858b</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ANS47</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>47</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>25.06.2020</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>04.07.2020</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>2</v>
+      </c>
+      <c r="K181" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>JSF, SEG-Y, JPG</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>47,1 Gb</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>180_ba7553e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ANS47</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>47</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>25.06.2020</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>04.07.2020</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>2</v>
+      </c>
+      <c r="K182" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Hypack project</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>23,1 Gb</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>181_fde6aa17</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ANS47</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>47</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>25.06.2020</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>04.07.2020</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>2</v>
+      </c>
+      <c r="K183" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Reson Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>4.52 Gb</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>182_d2a712d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ANS47</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>47</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>25.06.2020</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>04.07.2020</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>2</v>
+      </c>
+      <c r="K184" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Reson Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>CTD, SVP, NAV, журналы, треки, приказы и программа</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>177 Mb</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>183_8a939cd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AI56</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Академик Иоффе</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>56</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>19.08.2020</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>28.08.2020</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Ульянова М.О.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>2</v>
+      </c>
+      <c r="K185" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ, ИЭЗ Польши, ИЭЗ Швеции</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Hypack project, журналы, PrintScreen, моэаики (GeoTif)</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>15.6 Gb</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>184_5927acf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ASV51</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Академик Сергей Вавилов</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>51</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>30.06.2021</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>14.07.2021</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Ульянова М.О.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>2</v>
+      </c>
+      <c r="K186" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Юго-восточный и центральный р-н Балтийского моря, ИЭЗ РФ, ИЭЗ Швеции, FZ</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Kongsberg Simrad EA600</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>RAW, XYZ, Shape, журналы</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>785  Mb</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>185_113891bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ANS51</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>51</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>02.09.2021</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Ахманов</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>2</v>
+      </c>
+      <c r="K187" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Дудков И.Ю.</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>ЦМИ МГУ</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>SEB, переходный галс в Балтике</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Reson Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>PDS2000 projects, XTF</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>13.7 Gb</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>186_554dfda0</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ANS51</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>51</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>02.09.2021</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Ахманов</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Дудков И.Ю.</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>ЦМИ МГУ</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>SEB, переходный галс в Балтике</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>JSF, SEG-Y, JPG</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>1.83 Gb</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>187_6491c0ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ANS44</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>44</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>09.10.2019</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>25.10.2019</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Баширова Л.Д.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>2</v>
+      </c>
+      <c r="K189" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Матуль А.Г.</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Восточная тропическая Атлантика. Проход Кейн</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>сонарные данные  XTF, GeoTIF</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>7.6 Gb</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>188_8487fa1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>PSH131</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>131</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>30.03.2016</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>06.04.2016</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Hypack project, RAW, GeoTIF, Shape, PrintScreen, SVP</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>48.1 Gb</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>189_ea75f1bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>PSH131</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>131</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>30.03.2016</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>06.04.2016</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Kongsberg Simrad EA400</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>RAW Data, XYZ, PrintScreen, SVP</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>13.7 Gb</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>190_222ea41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>PSH131</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>131</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>30.03.2016</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>06.04.2016</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>SyQuest Bathy-2010</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>ODT, CSV</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>917 Mb</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>191_c6407e63</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>PSH132</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>132</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>11.06.2016</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>16.06.2016</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Hypack project, RAW, GeoTIF, Shape, PrintScreen, SVP</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>34.6 Gb</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>192_1390c8d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>PSH132</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>132</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>11.06.2016</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>16.06.2016</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>SyQuest Bathy-2010</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>ODT, CSV</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>545 Mb</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>193_5e88d8ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>PSH132</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>132</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>11.06.2016</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>16.06.2016</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Kongsberg Simrad EA400</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Hypack project, RAW Data, PrintScreen, SVP</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>20.9 Gb</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>194_908bd744</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>PSH133</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>133</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>16.07.2016</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>23.07.2016</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>Hypack project, RAW, GeoTIF, Shape, PrintScreen, SVP</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>46.9 Gb</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>195_ac2f0f61</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>PSH133</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>133</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>16.07.2016</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>23.07.2016</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Kongsberg Simrad EA400</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Hypack project, RAW, PrintScreen, SVP</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>51.6 Gb</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>196_de66c1c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>PSH134</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>134</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>27.10.2016</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>01.11.2016</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Ежов В.Е.</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>SyQuest Bathy-2010</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>ODT, CSV</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>998 Mb</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>197_90bc4c8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>PSH133</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>133</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>16.07.2016</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>23.07.2016</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Видеосъемка</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Super GNOM</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>MPG</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>863 Mb</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>198_c4756b84</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ANS32</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>32</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>02.08.2016</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>16.09.2016</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Пака В.Т.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>SEB. Борнхольмский, Слупский, Гданьский бассейны</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>JSF, SEG-Y</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>4.27 Gb</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>199_09f82f09</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ANS32</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>32</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>02.08.2016</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>16.09.2016</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Пака В.Т.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>1</v>
+      </c>
+      <c r="K201" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Крюков Д.А.</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>SEB. ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Hypack project, GeoTif, SVP, журнал</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>127 Gb</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>200_db299e28</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ANS32</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>32</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>02.08.2016</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>16.09.2016</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Пака В.Т.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>1-2 ???</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Reson Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>PDS2000</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>148 Gb</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>201_9c7a6ecc</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ANS32</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>32</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>02.08.2016</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>16.09.2016</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Пака В.Т.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>1-2 ???</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Reson Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Q-GIS project</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>458 Mb</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>202_9ad9d94a</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ANS32</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>32</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>02.08.2016</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>16.09.2016</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Пака В.Т.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1-2 ???</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Reson Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, XYZ, GRID</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>2.86 Gb</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>203_a4d600b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ANS33</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>33</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>18.10.2016</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>26.12.2016</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Сивков В.В.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Сухих Е.А.</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Атлантика, Балтика</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150, 8111</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>ArcGIS project, плигоны в GeoTIF</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>21 Gb</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>204_2d77b806</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ANS33</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>33</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>18.10.2016</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>26.12.2016</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Сивков В.В.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Сухих Е.А.</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Атлантика</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>PDS2000 projects, DTM</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>98.1 Gb</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>205_b3ef8fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ANS33</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>33</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>18.10.2016</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>26.12.2016</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Сивков В.В.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Сухих Е.А.</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Балтика</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Reson Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>PDS2000 projects, DTM</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>170 Gb</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>206_b307b28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ANS33</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>33</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>18.10.2016</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>26.12.2016</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Сивков В.В.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Сухих Е.А.</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Атлантика, Балтика</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150, 8111</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>ASCII, XYZ, NAV, журналы, программа</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>179 Mb</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>207_2f65c322</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ANS33</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>33</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>18.10.2016</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>26.12.2016</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Сивков В.В.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Сухих Е.А.</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Атлантика</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>PDS2000 projects, DTM</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>1.22 Gb</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>208_c82fe531</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ANS33</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>33</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>18.10.2016</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>26.12.2016</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Сивков В.В.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Сухих Е.А.</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Атлантика, Балтика</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 7150, 8111</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, XYZ, JPG</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>272 Mb</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>209_f13caa3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>ОЛЭ</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Kongsberg Simrad EA600</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>Hypack project (9 проектов)</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>1.41 Gb</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>210_94583569</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>Отчет PHG2015</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>1.62 Gb</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>211_93c401ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Hypack projects (разные)</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>20.9 Gb</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>212_9ed0b8c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>PSH131 ???</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>131</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>30.03.2016</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>06.04.2016</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Зверев</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Сейсмокоса</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Сейсмокомплекс на основе сейсмостанции ES-3000 Exploration Seismograph</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>SEG-Y, BMP, JPG</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>2.58 Gb</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>213_e7f38ce8</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ANS34</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>34</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>14.06.2017</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>08.07.2017</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>SEG-Y, JSF, SVP, журналы, навигация, отчеты</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>18.2 Gb</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>214_9a3537cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ANS34</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>34</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>14.06.2017</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>08.07.2017</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>PDS2000 projects, XTF, GeoTif, ESRI ASCII, JPG, DTM</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>33,6 Gb</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>215_67166f25</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ANS34</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>34</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>14.06.2017</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>08.07.2017</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>AUV Iver2</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>GeoTiff, PrintScreen</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>44 Mb</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>216_7186a0d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ANS34</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>34</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>14.06.2017</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>08.07.2017</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>508 Mb</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>217_8c98b78e</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ANS36</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>36</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>02.10.2017</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>21.10.2017</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Журналы, навигация, программа, отчет</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>450 Mb</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>218_553b2b56</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ANS36</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>36</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>02.10.2017</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>21.10.2017</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>EdgeTech 3300-HM</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>JSF, SEG-Y</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>19.1 Gb</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>219_e41c58ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ANS36</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>36</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>02.10.2017</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>21.10.2017</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>PDS2000 project, DTM, XTF</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>122 Gb</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>220_d5df85ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ANS36</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>36</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>02.10.2017</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>21.10.2017</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>1.33 Gb</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>221_67463d7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>PSH135</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Профессор Штокман</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>135</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>03.04.2017</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>07.04.2017</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>1</v>
+      </c>
+      <c r="K223" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>SEB, ИЭЗ РФ</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>ГЛБО</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Benthos C3D</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Сырые и обработанные</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>Hypack project, журналы</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>2.16 Gb</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>222_9d6254c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ANS34</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>34</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>14.06.2017</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>08.07.2017</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, Tiff</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>254 Mb</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>223_6c6ff675</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ANS35</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>35</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>14.07.2017</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>28.07.2017</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>1</v>
+      </c>
+      <c r="K225" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>7.21 Gb</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>224_157fc715</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ANS35</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>35</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>14.07.2017</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>28.07.2017</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Сергеев А.Ю.</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>FZ</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>3.8 Gb</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>225_6eac0050</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ANS36</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>36</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>02.10.2017</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>21.10.2017</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
+      <c r="K227" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Кречик В.А.</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>157 Mb</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>226_9a69f59f</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ANS37</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>37</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>23.10.2017</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>27.10.2017</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Крек А.В.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>2</v>
+      </c>
+      <c r="K228" t="n">
+        <v>6190001111732</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Данченков А.Р.</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>2.71 Gb</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>227_fb036c3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ANS34</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Академик Николай Страхов</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>34</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>14.06.2017</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>08.07.2017</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Щука С.А.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Reson SeaBat 8111</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>ESRI ASCII, XYZ</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>678 Mb</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>228_13b135e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ABP47</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Академик Борис Петров</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>47</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>16.09.2021</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>05.10.2021</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Луговой Н.Н.</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Профилограф</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Parasound P70</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>ASD, SEG-Y</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>255 Gb</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>229_16b369c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ABP48</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Академик Борис Петров</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>48</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>29.10.2021</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>12.11.2021</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>SEB</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Applanix</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>Необработанные</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>tracks csv</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>213 Mb</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>230_d95c775f</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" t="n">
+        <v>6190001111735</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Дорохов Д.В.</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>МЛЭ</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Обработанные</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>GeoTiff</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>49.6 Gb</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>231_345a1136</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
